--- a/部屋ID一覧.xlsx
+++ b/部屋ID一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -422,6 +422,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,6 +457,16 @@
           <t>分類</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>メモ（R8）</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,14 +479,11 @@
           <t>ふれあい広場</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -497,8 +506,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>アームロボット・ライントレーサー</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>電子機械科</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Em① アームロボットの実演、ライントレーサー、シーケンス制御（FA実習室）</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -508,7 +535,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>機械加工実習室</t>
+          <t>機械加工室</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,8 +548,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>旋盤の加工実演</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>機械科</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>M① 旋盤の加工実演（機械加工室）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -545,8 +590,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>マシニングセンタでプレート製作</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>機械科</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>M② マシニングセンターによるプレートの製作（計測実習室）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -569,8 +632,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -593,8 +654,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>溶接実演とバーベキューコンロ製作</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>機械科</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>M③ 溶接実演とバーベキューコンロの製作（溶接実習室）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -617,8 +696,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -641,8 +718,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>エンジンの分解・組立</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>機械科</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>M④ エンジンの分解・組立（原動機実験室）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -665,8 +760,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ミニ工場見学</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>材料技術科</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Z① 旋盤・NCフライス盤を使って製作（切削加工室）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -689,8 +802,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -713,8 +824,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -737,8 +846,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>大会・技能検定の課題紹介</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>専攻科</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>S③ 若年者ものづくり競技会の課題、技能検定2級の課題、数値制御工作機械の作品</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -761,8 +888,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -785,8 +910,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -809,8 +932,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LED点滅装置と単軸テーブル</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>電子機械科</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Em② LED点滅装置と単軸テーブルの展示（電気実習室）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -833,8 +974,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -857,8 +996,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -881,8 +1018,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3D CADと3Dプリンタ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>電子機械科</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Em④ 3D CADの演習と3Dプリンタの実演（製図室）</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -905,8 +1060,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -929,8 +1082,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>化学縁日</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>材料技術科</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Z② 液体窒素を使った実験ほか（セラミック室）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -953,8 +1124,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -977,8 +1146,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>射出成形・キーホルダー製作</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>材料技術科</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Z③ 射出成形機の運転、プラ板キーホルダー・黒工キーホルダーの製作と配布（高分子材料室）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1001,8 +1188,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1015,14 +1200,11 @@
           <t>食物実習室</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1045,8 +1227,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NC旋盤の実演</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>電子機械科</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Em③ NC旋盤の実演（制御実習室）</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1059,14 +1259,31 @@
           <t>材料試験室</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>鉄筋の引張試験</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>土木科</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>C① 鉄筋の引張試験（材料試験室）</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1079,14 +1296,11 @@
           <t>柔剣道場</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1099,14 +1313,11 @@
           <t>薬品器材室</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1119,14 +1330,11 @@
           <t>施工実習室</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1139,14 +1347,31 @@
           <t>工作工事実習室</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>電気のつくりかた・電磁石つり</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>電気科</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>E① 各種発電の原理／E② 電気で磁石をつくって釣りしよう／E④ シーケンスってなに？（工作工事実習室）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1159,14 +1384,31 @@
           <t>製図実習室</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>電気工事体験</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>電気科</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>E③ 配線結線、ものづくりコンテストの実演（製図実習室）</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1189,8 +1431,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1203,14 +1443,11 @@
           <t>北棟昇降口</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1233,8 +1470,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>カラダ探し（電子機械科3年）</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>電子機械科</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>電子機械科3年のクラス企画</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1257,8 +1512,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>めんずお茶会クラブ（機械科3年）</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>食べ物</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>機械科</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>機械科3年のクラス企画</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1281,8 +1554,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>メイド喫茶・カジノ（電子科3年）</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>食べ物</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>電子科</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>電子科3年「推進力」メイド喫茶、ベイブレード広場、カジノ</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1305,8 +1596,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>コスプレ喫茶（土木科3年）</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>食べ物</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>土木科</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>土木科3年のクラス企画。コスプレ喫茶、フォトスポット</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1329,8 +1638,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1353,8 +1660,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ドローンの操縦体験</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>土木科</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>C③ ドローンの操縦体験（測量実習室）</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1377,8 +1702,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>電気工事業組合の展示</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>電気科</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>E⑤ 電気工事業組合の展示（自動制御実習室）</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1401,8 +1744,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1425,8 +1766,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1439,14 +1778,26 @@
           <t>第一体育館</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ステージ（第一体育館）</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>カラオケ大会（1日目・生徒会）、吹奏楽部「一心同音」（23日のみ）、1学年音楽選択者による合唱</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1459,14 +1810,11 @@
           <t>合成化学実習室</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1479,14 +1827,11 @@
           <t>工作実習室①</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1499,14 +1844,11 @@
           <t>工作実習室②</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1529,8 +1871,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1553,8 +1893,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1567,14 +1905,26 @@
           <t>南棟昇降口</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>受付（南棟昇降口）</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>一般の方の受付。来賓の方は本館玄関の来賓受付へ</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1597,8 +1947,21 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PTA母親委員会</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>内容は決まりしだいお知らせします（選択3）</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1621,8 +1984,21 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>射的・仮装シールラリー（生徒会）</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>10月24日（土）のみ（DXルーム）</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1642,11 +2018,9 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1669,8 +2043,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1693,8 +2065,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1717,8 +2087,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1741,8 +2109,6 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1755,14 +2121,11 @@
           <t>ボクシング場</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1775,14 +2138,26 @@
           <t>第二体育館</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>飲食ブース（第二体育館）</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>食べ物</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>飲食はここで。キッチンカーは第二体育館の前</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1795,14 +2170,26 @@
           <t>記念館</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>記念館公開（同窓会）</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>黒工の資料展示</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1815,24 +2202,21 @@
           <t>北桜会館</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1X-01</t>
+          <t>1F-60</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>測量・土質準備室</t>
+          <t>屋外特設会場</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1842,21 +2226,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>建設機材の運転体験</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>土木科</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>C② 屋外特設会場。雨天中止・小雨決行</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1X-02</t>
+          <t>1F-61</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>玄関</t>
+          <t>キッチンカー出店場所</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1866,61 +2268,78 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>キッチンカー</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>食べ物</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>業者による販売。食べる場所は第二体育館の飲食ブース</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1X-03</t>
+          <t>1X-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>北棟外部非常階段</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>測量・土質準備室</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>土木科実習棟</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>控え</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1X-04</t>
+          <t>1X-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ボイラー 室</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>玄関</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>本館</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>控え</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1X-05</t>
+          <t>1X-03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>校長室</t>
+          <t>北棟外部非常階段</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1933,18 +2352,16 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1X-06</t>
+          <t>1X-04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>体育準備室</t>
+          <t>ボイラー 室</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1957,18 +2374,16 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1X-07</t>
+          <t>1X-05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>保健室</t>
+          <t>校長室</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1981,43 +2396,43 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1X-08</t>
+          <t>1X-06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>部室</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>体育準備室</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>南教室棟</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>控え</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1X-09</t>
+          <t>1X-07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>機械科準備室</t>
+          <t>保健室</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>電子機械科実習棟</t>
+          <t>本館</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2025,18 +2440,16 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1X-10</t>
+          <t>1X-08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>製図準備室</t>
+          <t>部室</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2049,23 +2462,21 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1X-11</t>
+          <t>1X-09</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>更衣室</t>
+          <t>機械科準備室</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>本館</t>
+          <t>電子機械科実習棟</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2073,23 +2484,21 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1X-12</t>
+          <t>1X-10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>事務室</t>
+          <t>製図準備室</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>本館</t>
+          <t>機械科実習棟</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2097,23 +2506,21 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1X-13</t>
+          <t>1X-11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>計測準備室</t>
+          <t>更衣室</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>専攻科棟</t>
+          <t>本館</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2121,18 +2528,16 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1X-14</t>
+          <t>1X-12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>普通科職員室</t>
+          <t>事務室</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2145,23 +2550,21 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1X-15</t>
+          <t>1X-13</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>磁気シールド</t>
+          <t>計測準備室</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>電子科実習棟</t>
+          <t>専攻科棟</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2169,18 +2572,16 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1X-16</t>
+          <t>1X-14</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>中会議室</t>
+          <t>普通科職員室</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2193,23 +2594,21 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1X-17</t>
+          <t>1X-15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>準備室</t>
+          <t>磁気シールド</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>材料技術科実習棟</t>
+          <t>電子科実習棟</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2217,43 +2616,43 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1X-18</t>
+          <t>1X-16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>工作工事準備室</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>中会議室</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>本館</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>控え</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1X-19</t>
+          <t>1X-17</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>物品庫</t>
+          <t>準備室</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>南教室棟</t>
+          <t>材料技術科実習棟</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2261,18 +2660,16 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1X-20</t>
+          <t>1X-18</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>応接室</t>
+          <t>工作工事準備室</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2285,23 +2682,21 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1X-21</t>
+          <t>1X-19</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>準備室</t>
+          <t>物品庫</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>家庭科実習棟</t>
+          <t>南教室棟</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2309,23 +2704,21 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1X-22</t>
+          <t>1X-20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>鋳造準備室</t>
+          <t>応接室</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>機械科実習棟</t>
+          <t>本館</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2333,23 +2726,21 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1X-23</t>
+          <t>1X-21</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>給湯室</t>
+          <t>準備室</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>本館</t>
+          <t>家庭科実習棟</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2357,43 +2748,43 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1X-24</t>
+          <t>1X-22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>工業科職員室</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>鋳造準備室</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>機械科実習棟</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
           <t>控え</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1X-25</t>
+          <t>1X-23</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>自動制御準備室</t>
+          <t>給湯室</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>専攻科棟</t>
+          <t>本館</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2401,18 +2792,16 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1X-26</t>
+          <t>1X-24</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>書庫</t>
+          <t>工業科職員室</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2425,23 +2814,21 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1X-27</t>
+          <t>1X-25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>進路指導応接室</t>
+          <t>自動制御準備室</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>本館</t>
+          <t>専攻科棟</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2449,18 +2836,16 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1X-29</t>
+          <t>1X-26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>耐火書庫</t>
+          <t>書庫</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2473,18 +2858,16 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1X-30</t>
+          <t>1X-27</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ＰＴＡ同窓会</t>
+          <t>進路指導応接室</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2497,23 +2880,21 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1X-31</t>
+          <t>1X-29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>電気機器準備室</t>
+          <t>耐火書庫</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>電気科実習棟</t>
+          <t>本館</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2521,43 +2902,43 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1X-32</t>
+          <t>1X-30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>体育科職員室</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>ＰＴＡ同窓会</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>本館</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>控え</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1X-34</t>
+          <t>1X-31</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ロッカー</t>
+          <t>電気機器準備室</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>本館</t>
+          <t>電気科実習棟</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2565,118 +2946,106 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2F-01</t>
+          <t>1X-32</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>土木情報実習室</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>体育科職員室</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+          <t>控え</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2F-02</t>
+          <t>1X-34</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CAD実習室</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>ロッカー</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>本館</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+          <t>控え</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2F-03</t>
+          <t>2F-01</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>通信実習室</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>土木情報実習室</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2F-04</t>
+          <t>2F-02</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>電子機器室</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>CAD実習室</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2F-05</t>
+          <t>2F-03</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>電気磁気室</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>通信実習室</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2F-06</t>
+          <t>2F-04</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>電子機２</t>
+          <t>電子機器室</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2689,18 +3058,31 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>企業ブース（電子機2教室）</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2F-07</t>
+          <t>2F-05</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>機械２</t>
+          <t>電気磁気室</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2713,18 +3095,31 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>企業ブース（機械2教室）</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2F-08</t>
+          <t>2F-06</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>材料２</t>
+          <t>電子機２</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2737,18 +3132,31 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>企業ブース（電子機2教室）</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2F-09</t>
+          <t>2F-07</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>土木２</t>
+          <t>機械２</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2761,23 +3169,36 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>企業ブース（機械2教室）</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2F-10</t>
+          <t>2F-08</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>製図室</t>
+          <t>材料２</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>土木科実習棟</t>
+          <t>北教室棟</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2785,23 +3206,36 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>企業ブース（材料2教室）</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2F-11</t>
+          <t>2F-09</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>情報応用室</t>
+          <t>土木２</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>土木科実習棟</t>
+          <t>北教室棟</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2809,23 +3243,36 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>企業ブース（土木2教室）</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2F-12</t>
+          <t>2F-10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>計測実習室</t>
+          <t>製図室</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>電子科実習棟</t>
+          <t>土木科実習棟</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2833,23 +3280,41 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>電子科を知ろう！</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>電子科</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>EL① 電子科の学習と進路の紹介（計測実習室）</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2F-13</t>
+          <t>2F-11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>電子計算機室</t>
+          <t>情報応用室</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>電子科実習棟</t>
+          <t>土木科実習棟</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2857,78 +3322,157 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>電子科を知ろう！（電子計算機室）</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>電子科</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>EL① 電子科の学習と進路の紹介（電子計算機室）</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2F-14</t>
+          <t>2F-12</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>電気実習室</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>計測実習室</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>電子科実習棟</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>電子科を知ろう！</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>電子科</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>EL① 電子科の学習と進路の紹介（計測実習室）</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2F-15</t>
+          <t>2F-13</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>制御実習室</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>電子計算機室</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>電子科実習棟</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>電子科を知ろう！（電子計算機室）</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>電子科</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>EL① 電子科の学習と進路の紹介（電子計算機室）</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2F-16</t>
+          <t>2F-14</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>専攻科１年</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>電気実習室</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>専攻科の紹介・レーザー加工</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>専攻科</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>S① 紹介映像、実習装置の展示と体験、岩手大学・デンソー岩手での作品展示、レーザー加工機でコースター製作</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2F-17</t>
+          <t>2F-15</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>電気３</t>
+          <t>制御実習室</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2941,18 +3485,26 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>新科紹介</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2F-18</t>
+          <t>2F-16</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>電子３</t>
+          <t>専攻科１年</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2965,18 +3517,31 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>無線の世界を体験しよう（無線部）</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>無線・フィギュア展示、ドローン体験など</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2F-19</t>
+          <t>2F-17</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>選択②</t>
+          <t>電気３</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2989,18 +3554,31 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>新科紹介</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>動画放映、用具・部の歴史の展示</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2F-20</t>
+          <t>2F-18</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>選択①</t>
+          <t>電子３</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3013,23 +3591,36 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>無線の世界を体験しよう（無線部）</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>無線・フィギュア展示、ドローン体験など</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2F-21</t>
+          <t>2F-19</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>専攻科２年</t>
+          <t>選択②</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>専攻科棟</t>
+          <t>南教室棟</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3037,23 +3628,41 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>水泳部</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>専攻科</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>動画放映、用具・部の歴史の展示</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2F-22</t>
+          <t>2F-20</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>化学分析実習室</t>
+          <t>選択①</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>専攻科棟</t>
+          <t>南教室棟</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3061,58 +3670,95 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>写真部</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>フォトスポット、ストリートスナップ、写真展示</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2F-23</t>
+          <t>2F-21</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>理科教室</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>専攻科２年</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>専攻科棟</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>修了研究・グループ研究の作品</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>専攻科</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>S② 修了研究作品・グループ研究作品の展示（専攻科2年HR）</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2F-24</t>
+          <t>2F-22</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>図書室</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>化学分析実習室</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>専攻科棟</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>表示</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2F-25</t>
+          <t>2F-23</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>化学実験室</t>
+          <t>理科教室</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3122,21 +3768,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2F-26</t>
+          <t>2F-24</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>物理実験室</t>
+          <t>図書室</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3146,41 +3790,41 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2F-27</t>
+          <t>2F-25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>会議室</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>化学実験室</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>本館</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2X-01</t>
+          <t>2F-26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>物理準備室</t>
+          <t>物理実験室</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3190,41 +3834,36 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2X-02</t>
+          <t>2F-27</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>教育支援談室</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>会議室</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2X-03</t>
+          <t>2F-28</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>電子磁気準備室</t>
+          <t>2階廊下</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3234,41 +3873,56 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>美術・家庭科の作品展示</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2階廊下。美術の授業作品（てぬぐい）、ファスナーポーチ・ホームプロジェクト、美術部の作品</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2X-04</t>
+          <t>2X-01</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>更衣室</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>物理準備室</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>本館</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2X-05</t>
+          <t>2X-02</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>専攻科職員室</t>
+          <t>教育支援談室</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3278,61 +3932,58 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2X-06</t>
+          <t>2X-03</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>生徒会室</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
+          <t>電子磁気準備室</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>電子科実習棟</t>
+        </is>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>控え</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2X-08</t>
+          <t>2X-04</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>通信準備室</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>更衣室</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2X-09</t>
+          <t>2X-05</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>化学分析準備室</t>
+          <t>専攻科職員室</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3345,18 +3996,16 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2X-10</t>
+          <t>2X-06</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>司書室</t>
+          <t>生徒会室</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3369,58 +4018,55 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2X-11</t>
+          <t>2X-08</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>資料室</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
+          <t>通信準備室</t>
+        </is>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
           <t>控え</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2X-12</t>
+          <t>2X-09</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>無線部室</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
+          <t>化学分析準備室</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>専攻科棟</t>
+        </is>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
           <t>控え</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2X-13</t>
+          <t>2X-10</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>化学準備室</t>
+          <t>司書室</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3430,21 +4076,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2X-14</t>
+          <t>2X-11</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>暗室</t>
+          <t>資料室</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3457,18 +4101,16 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2X-15</t>
+          <t>2X-12</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>書庫</t>
+          <t>無線部室</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3481,90 +4123,127 @@
           <t>控え</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3F-01</t>
+          <t>2X-13</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>電子機１</t>
+          <t>化学準備室</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>北教室棟</t>
+          <t>本館</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>企業ブース（電子機1教室）</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3F-02</t>
+          <t>2X-14</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>機械１</t>
+          <t>暗室</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>北教室棟</t>
+          <t>電子科実習棟</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+          <t>控え</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>企業ブース（機械1教室）</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3F-03</t>
+          <t>2X-15</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>材料１</t>
+          <t>書庫</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>北教室棟</t>
+          <t>本館</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>企業ブース（材料1教室）</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3F-04</t>
+          <t>3F-01</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>土木１</t>
+          <t>電子機１</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3577,23 +4256,36 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>企業ブース（電子機1教室）</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3F-05</t>
+          <t>3F-02</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>電気２</t>
+          <t>機械１</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>南教室棟</t>
+          <t>北教室棟</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3601,23 +4293,36 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>企業ブース（機械1教室）</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3F-06</t>
+          <t>3F-03</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>電子２</t>
+          <t>材料１</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>南教室棟</t>
+          <t>北教室棟</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3625,23 +4330,36 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>企業ブース（材料1教室）</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3F-07</t>
+          <t>3F-04</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>電気１</t>
+          <t>土木１</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>南教室棟</t>
+          <t>北教室棟</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3649,18 +4367,31 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>企業ブース（土木1教室）</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>各企業の紹介と製品の展示</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3F-08</t>
+          <t>3F-05</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>電子１</t>
+          <t>電気２</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3673,23 +4404,21 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3F-09</t>
+          <t>3F-06</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>美術室</t>
+          <t>電子２</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>本館</t>
+          <t>南教室棟</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3697,23 +4426,21 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3F-10</t>
+          <t>3F-07</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>視聴覚室</t>
+          <t>電気１</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>本館</t>
+          <t>南教室棟</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3721,23 +4448,21 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3F-11</t>
+          <t>3F-08</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>音楽室</t>
+          <t>電子１</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>本館</t>
+          <t>南教室棟</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3745,18 +4470,16 @@
           <t>表示</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3F-12</t>
+          <t>3F-09</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CAI教室</t>
+          <t>美術室</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3766,21 +4489,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3X-01</t>
+          <t>3F-10</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CAI準備室 視聴覚準備室</t>
+          <t>視聴覚室</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3790,21 +4511,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3X-02</t>
+          <t>3F-11</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>更衣室</t>
+          <t>音楽室</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3814,21 +4533,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3X-03</t>
+          <t>3F-12</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>美術準備室</t>
+          <t>CAI教室</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3838,21 +4555,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3X-04</t>
+          <t>3X-01</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>資料室</t>
+          <t>CAI準備室 視聴覚準備室</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3862,35 +4577,147 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
+          <t>立入禁止</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>3X-02</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>更衣室</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>本館</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>立入禁止</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>3X-03</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>美術準備室</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>本館</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>立入禁止</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>建設機材の運転体験</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>体験</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>土木科</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>C② 屋外特設会場。雨天中止・小雨決行</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>3X-04</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>資料室</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>本館</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>立入禁止</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>キッチンカー</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>食べ物</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>業者による販売。食べる場所は第二体育館の飲食ブース</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>3X-05</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>暗室</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>本館</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>控え</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>立入禁止</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>美術・家庭科の作品展示</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>展示</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2階廊下。美術の授業作品（てぬぐい）、ファスナーポーチ・ホームプロジェクト、美術部の作品</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
